--- a/resources/templates/standard/L3100-04.xlsx
+++ b/resources/templates/standard/L3100-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>명 칭</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>기기번호</t>
+  </si>
+  <si>
+    <t>{{companyLogo}}</t>
   </si>
   <si>
     <t>NO</t>
@@ -992,7 +995,9 @@
       <c r="BN2" s="5"/>
     </row>
     <row r="3" ht="150" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
+      <c r="A3" s="8" t="s">
+        <v>4</v>
+      </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -1129,17 +1134,17 @@
     </row>
     <row r="5" ht="26.1" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>
@@ -1152,7 +1157,7 @@
       <c r="P5" s="13"/>
       <c r="Q5" s="13"/>
       <c r="R5" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S5" s="15">
         <v>1</v>
@@ -1270,14 +1275,14 @@
         <v>1</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
@@ -1290,7 +1295,7 @@
       <c r="P6" s="19"/>
       <c r="Q6" s="19"/>
       <c r="R6" s="20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S6" s="21"/>
       <c r="T6" s="21"/>
@@ -1414,14 +1419,14 @@
         <v>2</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
       <c r="G8" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
@@ -1434,7 +1439,7 @@
       <c r="P8" s="19"/>
       <c r="Q8" s="19"/>
       <c r="R8" s="20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S8" s="21"/>
       <c r="T8" s="21"/>
@@ -1558,14 +1563,14 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
       <c r="G10" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="19"/>
       <c r="I10" s="19"/>
@@ -1578,7 +1583,7 @@
       <c r="P10" s="19"/>
       <c r="Q10" s="19"/>
       <c r="R10" s="20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S10" s="21"/>
       <c r="T10" s="21"/>
@@ -1702,14 +1707,14 @@
         <v>4</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" s="23"/>
       <c r="I12" s="23"/>
@@ -1722,7 +1727,7 @@
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
       <c r="R12" s="20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S12" s="21"/>
       <c r="T12" s="21"/>
@@ -1843,7 +1848,7 @@
     </row>
     <row r="14" ht="26.1" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="24"/>
@@ -1863,7 +1868,7 @@
       <c r="Q14" s="24"/>
       <c r="R14" s="24"/>
       <c r="S14" s="25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T14" s="25"/>
       <c r="U14" s="25"/>
@@ -1915,7 +1920,7 @@
     </row>
     <row r="15" ht="26.1" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="26"/>
       <c r="C15" s="26"/>
@@ -1935,7 +1940,7 @@
       <c r="Q15" s="26"/>
       <c r="R15" s="26"/>
       <c r="S15" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T15" s="27"/>
       <c r="U15" s="27"/>
@@ -1987,7 +1992,7 @@
     </row>
     <row r="16" ht="26.1" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
@@ -2007,7 +2012,7 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T16" s="29"/>
       <c r="U16" s="29"/>
@@ -2016,7 +2021,7 @@
       <c r="X16" s="29"/>
       <c r="Y16" s="29"/>
       <c r="Z16" s="29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA16" s="29"/>
       <c r="AB16" s="29"/>
@@ -2025,7 +2030,7 @@
       <c r="AE16" s="29"/>
       <c r="AF16" s="29"/>
       <c r="AG16" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH16" s="29"/>
       <c r="AI16" s="29"/>
@@ -2034,7 +2039,7 @@
       <c r="AL16" s="29"/>
       <c r="AM16" s="29"/>
       <c r="AN16" s="29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO16" s="29"/>
       <c r="AP16" s="29"/>
@@ -2043,7 +2048,7 @@
       <c r="AS16" s="29"/>
       <c r="AT16" s="29"/>
       <c r="AU16" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV16" s="30"/>
       <c r="AW16" s="30"/>
@@ -2067,7 +2072,7 @@
     </row>
     <row r="17" ht="26.1" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
@@ -3210,20 +3215,20 @@
       <c r="AZ33" s="5"/>
       <c r="BA33" s="5"/>
       <c r="BB33" s="34" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC33" s="35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD33" s="35"/>
       <c r="BE33" s="35"/>
       <c r="BF33" s="35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BG33" s="35"/>
       <c r="BH33" s="35"/>
       <c r="BI33" s="35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BJ33" s="35"/>
       <c r="BK33" s="35"/>
